--- a/tuan-02/Domain D/Business_Rules_Domain_D.xlsx
+++ b/tuan-02/Domain D/Business_Rules_Domain_D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lehoa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C592F0B2-0AB2-4040-9B25-FB83BACB3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E547A00-1102-43DB-9B86-47BBF4CA6468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
   <si>
     <t>Mã</t>
   </si>
@@ -99,7 +99,7 @@
     <t>Mọi bước ghi/đọc qty (nhập, xuất, điều chỉnh, hiển thị)</t>
   </si>
   <si>
-    <t>Business Rule domain C: "Mọi số lượng lưu trong inventory và stock_ledger phải quy đổi về Base UOM"</t>
+    <t>Business Rule domain C (BR-C-01): "Mọi số lượng lưu trong inventory và stock_ledger phải quy đổi về Base UOM"</t>
   </si>
   <si>
     <t>BR-D-06</t>
@@ -126,7 +126,7 @@
     <t>BR-D-08</t>
   </si>
   <si>
-    <t>Chỉ location có location_type = BIN mới được phép có dòng trong inventory; các loại khác (RECV, QC, DAMAGED...) xử lý riêng theo domain B.</t>
+    <t>Chỉ location có location_type = BIN mới được phép có dòng trong inventory; các cấp ZONE/AISLE/RACK không trực tiếp chứa tồn.</t>
   </si>
   <si>
     <t>Khi tạo/cập nhật dòng inventory</t>
@@ -135,22 +135,46 @@
     <t>BR-D-09</t>
   </si>
   <si>
-    <t>lot_no và expiry_date chỉ được yêu cầu nhập khi skus.is_lot_tracked = true; nếu false thì để trống.</t>
+    <t>lot_no và expiry_date chỉ được yêu cầu nhập khi skus.is_lot_tracked = true; nếu false thì để trống (NULL).</t>
   </si>
   <si>
     <t>Form/API nhập hàng (Inbound) và điều chỉnh tồn kho</t>
   </si>
   <si>
-    <t xml:space="preserve"> không cho phép tồn âm tạm thời</t>
-  </si>
-  <si>
-    <t>không xóa cứng dữ liệu đã phát sinh giao dịch</t>
-  </si>
-  <si>
-    <t>cần domain B xác nhận danh sách location_type chính thức</t>
-  </si>
-  <si>
-    <t>cờ is_lot_tracked do domain C định nghĩa trên bảng skus</t>
+    <t>Điểm nối C↔D — cờ is_lot_tracked do domain C định nghĩa trên bảng skus</t>
+  </si>
+  <si>
+    <t>BR-D-10</t>
+  </si>
+  <si>
+    <t>Khi tính tổng qty_available của 1 SKU trên nhiều vị trí (VD: hiển thị cho Viewer/kế toán), CHỈ cộng các dòng inventory tại location có is_pickable = true; loại trừ location có purpose = QC hoặc DAMAGED dù qty_on_hand tại đó &gt; 0.</t>
+  </si>
+  <si>
+    <t>API/màn hình tổng hợp tồn kho theo SKU (không phải theo 1 vị trí cụ thể)</t>
+  </si>
+  <si>
+    <t>Khớp BR-B-06 của domain B: "Tồn ở vị trí purpose = QC/DAMAGED không tính vào available"</t>
+  </si>
+  <si>
+    <t>BR-D-11</t>
+  </si>
+  <si>
+    <t>Hàng đang chuyển kho (in-transit) được ghi nhận tại 1 location đặc biệt có purpose = TRANSIT (đề xuất của domain D, chờ domain B xác nhận chính thức); không được coi in-transit là "mất tồn" hay để trống location_id.</t>
+  </si>
+  <si>
+    <t>Luồng Transfer giữa 2 kho, giai đoạn giữa TRANSFER_OUT và TRANSFER_IN</t>
+  </si>
+  <si>
+    <t>Trả lời câu hỏi domain B đặt ra trong Data Dictionary ("Hàng in-transit nằm ở đâu?") — cần domain B xác nhận trước khi chốt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không cho phép tồn âm tạm thời </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> không xóa cứng dữ liệu đã phát sinh giao dịch</t>
+  </si>
+  <si>
+    <t>tồn kho luôn gắn với vị trí vật lý cụ thể nhất</t>
   </si>
 </sst>
 </file>
@@ -506,13 +530,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -533,7 +557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -547,10 +571,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -567,7 +591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -584,7 +608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -601,7 +625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -618,7 +642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -635,7 +659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -649,10 +673,10 @@
         <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
@@ -666,10 +690,10 @@
         <v>34</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -683,7 +707,41 @@
         <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>41</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
